--- a/orglens_sample_template.xlsx
+++ b/orglens_sample_template.xlsx
@@ -655,7 +655,7 @@
         <v>pranav.singh.0001@example.com</v>
       </c>
       <c r="W3" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-C000001&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X3" t="str">
         <v/>
@@ -735,7 +735,7 @@
         <v>sandeep.das.0001@example.com</v>
       </c>
       <c r="W4" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-X000001&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X4" t="str">
         <v/>
@@ -815,7 +815,7 @@
         <v>swati.mehta.0002@example.com</v>
       </c>
       <c r="W5" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-X000002&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X5" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>maya.nair.0003@example.com</v>
       </c>
       <c r="W6" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-X000003&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X6" t="str">
         <v/>
@@ -975,7 +975,7 @@
         <v>sanjay.singh.0004@example.com</v>
       </c>
       <c r="W7" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-X000004&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X7" t="str">
         <v/>
@@ -1055,7 +1055,7 @@
         <v>kunal.desai.0005@example.com</v>
       </c>
       <c r="W8" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-X000005&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X8" t="str">
         <v/>
@@ -1135,7 +1135,7 @@
         <v>tanmay.joshi.0006@example.com</v>
       </c>
       <c r="W9" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-X000006&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X9" t="str">
         <v/>
@@ -1215,7 +1215,7 @@
         <v>madhuri.bhattacharya.0001@example.com</v>
       </c>
       <c r="W10" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000001&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X10" t="str">
         <v/>
@@ -1375,7 +1375,7 @@
         <v>siddharth.bhatt.0003@example.com</v>
       </c>
       <c r="W12" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000003&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X12" t="str">
         <v/>
@@ -1455,7 +1455,7 @@
         <v>deepak.kulkarni.0004@example.com</v>
       </c>
       <c r="W13" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000004&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X13" t="str">
         <v/>
@@ -1535,7 +1535,7 @@
         <v>tanmay.mukherjee.0005@example.com</v>
       </c>
       <c r="W14" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000005&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X14" t="str">
         <v/>
@@ -1615,7 +1615,7 @@
         <v>isha.saxena.0006@example.com</v>
       </c>
       <c r="W15" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000006&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X15" t="str">
         <v/>
@@ -1695,7 +1695,7 @@
         <v>pooja.sharma.0007@example.com</v>
       </c>
       <c r="W16" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000007&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X16" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>suresh.chatterjee.0008@example.com</v>
       </c>
       <c r="W17" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000008&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X17" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>roshni.singh.0009@example.com</v>
       </c>
       <c r="W18" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000009&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X18" t="str">
         <v/>
@@ -1935,7 +1935,7 @@
         <v>kavya.kapoor.0010@example.com</v>
       </c>
       <c r="W19" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000010&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X19" t="str">
         <v/>
@@ -2015,7 +2015,7 @@
         <v>swati.reddy.0011@example.com</v>
       </c>
       <c r="W20" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000011&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X20" t="str">
         <v/>
@@ -2095,7 +2095,7 @@
         <v>neha.krishnan.0012@example.com</v>
       </c>
       <c r="W21" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000012&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X21" t="str">
         <v/>
@@ -2175,7 +2175,7 @@
         <v>aditya.iyer.0013@example.com</v>
       </c>
       <c r="W22" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000013&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X22" t="str">
         <v/>
@@ -2255,7 +2255,7 @@
         <v>yash.bhatt.0014@example.com</v>
       </c>
       <c r="W23" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000014&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X23" t="str">
         <v/>
@@ -2335,7 +2335,7 @@
         <v>ritu.mehta.0015@example.com</v>
       </c>
       <c r="W24" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000015&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X24" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>kavya.pillai.0016@example.com</v>
       </c>
       <c r="W25" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000016&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X25" t="str">
         <v/>
@@ -2495,7 +2495,7 @@
         <v>asha.patel.0017@example.com</v>
       </c>
       <c r="W26" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000017&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X26" t="str">
         <v/>
@@ -2575,7 +2575,7 @@
         <v>pooja.choudhury.0018@example.com</v>
       </c>
       <c r="W27" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000018&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X27" t="str">
         <v/>
@@ -2655,7 +2655,7 @@
         <v>rahul.gupta.0019@example.com</v>
       </c>
       <c r="W28" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000019&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X28" t="str">
         <v/>
@@ -2735,7 +2735,7 @@
         <v>anil.choudhury.0020@example.com</v>
       </c>
       <c r="W29" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000020&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X29" t="str">
         <v/>
@@ -2815,7 +2815,7 @@
         <v>kirti.gupta.0021@example.com</v>
       </c>
       <c r="W30" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000021&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X30" t="str">
         <v/>
@@ -2895,7 +2895,7 @@
         <v>aditya.bhatt.0022@example.com</v>
       </c>
       <c r="W31" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000022&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X31" t="str">
         <v/>
@@ -2975,7 +2975,7 @@
         <v>rahul.gupta.0023@example.com</v>
       </c>
       <c r="W32" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000023&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X32" t="str">
         <v/>
@@ -3055,7 +3055,7 @@
         <v>ritu.trivedi.0024@example.com</v>
       </c>
       <c r="W33" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000024&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X33" t="str">
         <v/>
@@ -3135,7 +3135,7 @@
         <v>aditya.chatterjee.0025@example.com</v>
       </c>
       <c r="W34" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000025&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X34" t="str">
         <v/>
@@ -3215,7 +3215,7 @@
         <v>shweta.verma.0026@example.com</v>
       </c>
       <c r="W35" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000026&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X35" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>sunita.agarwal.0027@example.com</v>
       </c>
       <c r="W36" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000027&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X36" t="str">
         <v/>
@@ -3375,7 +3375,7 @@
         <v>asha.agarwal.0028@example.com</v>
       </c>
       <c r="W37" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000028&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X37" t="str">
         <v/>
@@ -3455,7 +3455,7 @@
         <v>isha.bhattacharya.0029@example.com</v>
       </c>
       <c r="W38" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000029&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X38" t="str">
         <v/>
@@ -3535,7 +3535,7 @@
         <v>vivek.das.0030@example.com</v>
       </c>
       <c r="W39" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-V000030&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X39" t="str">
         <v/>
@@ -3855,7 +3855,7 @@
         <v>pooja.sharma.0001@example.com</v>
       </c>
       <c r="W43" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000001&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X43" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>priya.das.0002@example.com</v>
       </c>
       <c r="W44" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000002&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X44" t="str">
         <v/>
@@ -4015,7 +4015,7 @@
         <v>yash.verma.0003@example.com</v>
       </c>
       <c r="W45" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000003&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X45" t="str">
         <v/>
@@ -4095,7 +4095,7 @@
         <v>ramesh.joshi.0004@example.com</v>
       </c>
       <c r="W46" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000004&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X46" t="str">
         <v/>
@@ -4175,7 +4175,7 @@
         <v>ramesh.verma.0005@example.com</v>
       </c>
       <c r="W47" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000005&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X47" t="str">
         <v/>
@@ -4255,7 +4255,7 @@
         <v>vivek.krishnan.0006@example.com</v>
       </c>
       <c r="W48" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000006&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X48" t="str">
         <v/>
@@ -4415,7 +4415,7 @@
         <v>madhuri.malhotra.0008@example.com</v>
       </c>
       <c r="W50" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000008&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X50" t="str">
         <v/>
@@ -4495,7 +4495,7 @@
         <v>shweta.saxena.0009@example.com</v>
       </c>
       <c r="W51" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000009&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X51" t="str">
         <v/>
@@ -4575,7 +4575,7 @@
         <v>ramesh.gupta.0010@example.com</v>
       </c>
       <c r="W52" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000010&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X52" t="str">
         <v/>
@@ -4655,7 +4655,7 @@
         <v>asha.choudhury.0011@example.com</v>
       </c>
       <c r="W53" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000011&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X53" t="str">
         <v/>
@@ -4735,7 +4735,7 @@
         <v>sandeep.trivedi.0012@example.com</v>
       </c>
       <c r="W54" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000012&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X54" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>aarti.joshi.0013@example.com</v>
       </c>
       <c r="W55" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000013&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X55" t="str">
         <v/>
@@ -4895,7 +4895,7 @@
         <v>divya.menon.0014@example.com</v>
       </c>
       <c r="W56" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000014&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X56" t="str">
         <v/>
@@ -4975,7 +4975,7 @@
         <v>vivek.gupta.0015@example.com</v>
       </c>
       <c r="W57" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000015&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X57" t="str">
         <v/>
@@ -5055,7 +5055,7 @@
         <v>geeta.malhotra.0016@example.com</v>
       </c>
       <c r="W58" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000016&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X58" t="str">
         <v/>
@@ -5135,7 +5135,7 @@
         <v>sunita.verma.0017@example.com</v>
       </c>
       <c r="W59" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000017&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X59" t="str">
         <v/>
@@ -5215,7 +5215,7 @@
         <v>aarti.sharma.0018@example.com</v>
       </c>
       <c r="W60" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000018&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X60" t="str">
         <v/>
@@ -5295,7 +5295,7 @@
         <v>vikram.kulkarni.0019@example.com</v>
       </c>
       <c r="W61" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000019&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X61" t="str">
         <v/>
@@ -5375,7 +5375,7 @@
         <v>shweta.menon.0020@example.com</v>
       </c>
       <c r="W62" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000020&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X62" t="str">
         <v/>
@@ -5455,7 +5455,7 @@
         <v>isha.das.0021@example.com</v>
       </c>
       <c r="W63" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000021&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X63" t="str">
         <v/>
@@ -5535,7 +5535,7 @@
         <v>tara.bhatt.0022@example.com</v>
       </c>
       <c r="W64" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000022&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X64" t="str">
         <v/>
@@ -5615,7 +5615,7 @@
         <v>ramesh.nair.0023@example.com</v>
       </c>
       <c r="W65" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000023&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X65" t="str">
         <v/>
@@ -5695,7 +5695,7 @@
         <v>pallavi.singh.0024@example.com</v>
       </c>
       <c r="W66" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000024&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X66" t="str">
         <v/>
@@ -5775,7 +5775,7 @@
         <v>aditya.tiwari.0025@example.com</v>
       </c>
       <c r="W67" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000025&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X67" t="str">
         <v/>
@@ -5855,7 +5855,7 @@
         <v>megha.banerjee.0026@example.com</v>
       </c>
       <c r="W68" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000026&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X68" t="str">
         <v/>
@@ -5935,7 +5935,7 @@
         <v>pallavi.chatterjee.0027@example.com</v>
       </c>
       <c r="W69" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000027&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X69" t="str">
         <v/>
@@ -6015,7 +6015,7 @@
         <v>madhuri.banerjee.0028@example.com</v>
       </c>
       <c r="W70" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000028&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X70" t="str">
         <v/>
@@ -6095,7 +6095,7 @@
         <v>anjali.bhatt.0029@example.com</v>
       </c>
       <c r="W71" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000029&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X71" t="str">
         <v/>
@@ -6175,7 +6175,7 @@
         <v>anjali.trivedi.0030@example.com</v>
       </c>
       <c r="W72" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000030&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X72" t="str">
         <v/>
@@ -6255,7 +6255,7 @@
         <v>aman.desai.0031@example.com</v>
       </c>
       <c r="W73" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000031&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X73" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>vikram.desai.0032@example.com</v>
       </c>
       <c r="W74" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000032&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X74" t="str">
         <v/>
@@ -6415,7 +6415,7 @@
         <v>arjun.singh.0033@example.com</v>
       </c>
       <c r="W75" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000033&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X75" t="str">
         <v/>
@@ -6495,7 +6495,7 @@
         <v>sneha.krishnan.0034@example.com</v>
       </c>
       <c r="W76" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000034&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X76" t="str">
         <v/>
@@ -6575,7 +6575,7 @@
         <v>manoj.verma.0035@example.com</v>
       </c>
       <c r="W77" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000035&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X77" t="str">
         <v/>
@@ -6735,7 +6735,7 @@
         <v>anil.menon.0037@example.com</v>
       </c>
       <c r="W79" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000037&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X79" t="str">
         <v/>
@@ -6815,7 +6815,7 @@
         <v>anjali.bhatt.0038@example.com</v>
       </c>
       <c r="W80" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000038&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X80" t="str">
         <v/>
@@ -6895,7 +6895,7 @@
         <v>asha.bhatt.0039@example.com</v>
       </c>
       <c r="W81" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000039&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X81" t="str">
         <v/>
@@ -6975,7 +6975,7 @@
         <v>anil.sharma.0040@example.com</v>
       </c>
       <c r="W82" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000040&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X82" t="str">
         <v/>
@@ -7055,7 +7055,7 @@
         <v>tara.kulkarni.0041@example.com</v>
       </c>
       <c r="W83" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000041&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X83" t="str">
         <v/>
@@ -7135,7 +7135,7 @@
         <v>megha.kulkarni.0042@example.com</v>
       </c>
       <c r="W84" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000042&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X84" t="str">
         <v/>
@@ -7215,7 +7215,7 @@
         <v>anil.das.0043@example.com</v>
       </c>
       <c r="W85" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000043&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X85" t="str">
         <v/>
@@ -7295,7 +7295,7 @@
         <v>pooja.menon.0044@example.com</v>
       </c>
       <c r="W86" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000044&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X86" t="str">
         <v/>
@@ -7375,7 +7375,7 @@
         <v>kirti.reddy.0045@example.com</v>
       </c>
       <c r="W87" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000045&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X87" t="str">
         <v/>
@@ -7455,7 +7455,7 @@
         <v>siddharth.banerjee.0046@example.com</v>
       </c>
       <c r="W88" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000046&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X88" t="str">
         <v/>
@@ -7535,7 +7535,7 @@
         <v>karan.chatterjee.0047@example.com</v>
       </c>
       <c r="W89" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000047&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X89" t="str">
         <v/>
@@ -7615,7 +7615,7 @@
         <v>sneha.menon.0048@example.com</v>
       </c>
       <c r="W90" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000048&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X90" t="str">
         <v/>
@@ -7695,7 +7695,7 @@
         <v>anjali.chatterjee.0049@example.com</v>
       </c>
       <c r="W91" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000049&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X91" t="str">
         <v/>
@@ -7775,7 +7775,7 @@
         <v>geeta.kapoor.0050@example.com</v>
       </c>
       <c r="W92" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000050&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X92" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>ananya.trivedi.0051@example.com</v>
       </c>
       <c r="W93" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000051&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X93" t="str">
         <v/>
@@ -7935,7 +7935,7 @@
         <v>ramesh.mukherjee.0052@example.com</v>
       </c>
       <c r="W94" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000052&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X94" t="str">
         <v/>
@@ -8015,7 +8015,7 @@
         <v>sanjay.malhotra.0053@example.com</v>
       </c>
       <c r="W95" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000053&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X95" t="str">
         <v/>
@@ -8095,7 +8095,7 @@
         <v>sandeep.tiwari.0054@example.com</v>
       </c>
       <c r="W96" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000054&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X96" t="str">
         <v/>
@@ -8255,7 +8255,7 @@
         <v>kavya.bhatt.0056@example.com</v>
       </c>
       <c r="W98" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000056&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X98" t="str">
         <v/>
@@ -8335,7 +8335,7 @@
         <v>aman.choudhury.0057@example.com</v>
       </c>
       <c r="W99" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000057&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X99" t="str">
         <v/>
@@ -8415,7 +8415,7 @@
         <v>siddharth.sharma.0058@example.com</v>
       </c>
       <c r="W100" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000058&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X100" t="str">
         <v/>
@@ -8495,7 +8495,7 @@
         <v>suresh.saxena.0059@example.com</v>
       </c>
       <c r="W101" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000059&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X101" t="str">
         <v/>
@@ -8655,7 +8655,7 @@
         <v>anil.mehta.0061@example.com</v>
       </c>
       <c r="W103" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000061&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X103" t="str">
         <v/>
@@ -8735,7 +8735,7 @@
         <v>aarti.kulkarni.0062@example.com</v>
       </c>
       <c r="W104" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000062&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X104" t="str">
         <v/>
@@ -8815,7 +8815,7 @@
         <v>karan.krishnan.0063@example.com</v>
       </c>
       <c r="W105" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000063&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X105" t="str">
         <v/>
@@ -8895,7 +8895,7 @@
         <v>vivek.choudhury.0064@example.com</v>
       </c>
       <c r="W106" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000064&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X106" t="str">
         <v/>
@@ -8975,7 +8975,7 @@
         <v>kavya.singh.0065@example.com</v>
       </c>
       <c r="W107" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000065&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X107" t="str">
         <v/>
@@ -9055,7 +9055,7 @@
         <v>aditya.kapoor.0066@example.com</v>
       </c>
       <c r="W108" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000066&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X108" t="str">
         <v/>
@@ -9135,7 +9135,7 @@
         <v>neha.iyer.0067@example.com</v>
       </c>
       <c r="W109" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000067&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X109" t="str">
         <v/>
@@ -9215,7 +9215,7 @@
         <v>nikhil.kapoor.0068@example.com</v>
       </c>
       <c r="W110" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000068&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X110" t="str">
         <v/>
@@ -9295,7 +9295,7 @@
         <v>swati.desai.0069@example.com</v>
       </c>
       <c r="W111" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000069&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X111" t="str">
         <v/>
@@ -9375,7 +9375,7 @@
         <v>riya.reddy.0070@example.com</v>
       </c>
       <c r="W112" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000070&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X112" t="str">
         <v/>
@@ -9455,7 +9455,7 @@
         <v>maya.tiwari.0071@example.com</v>
       </c>
       <c r="W113" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000071&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X113" t="str">
         <v/>
@@ -9535,7 +9535,7 @@
         <v>arjun.malhotra.0072@example.com</v>
       </c>
       <c r="W114" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000072&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X114" t="str">
         <v/>
@@ -9695,7 +9695,7 @@
         <v>anil.bhandari.0074@example.com</v>
       </c>
       <c r="W116" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000074&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X116" t="str">
         <v/>
@@ -9775,7 +9775,7 @@
         <v>pallavi.bhandari.0075@example.com</v>
       </c>
       <c r="W117" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000075&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X117" t="str">
         <v/>
@@ -9855,7 +9855,7 @@
         <v>pranav.nair.0076@example.com</v>
       </c>
       <c r="W118" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000076&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X118" t="str">
         <v/>
@@ -9935,7 +9935,7 @@
         <v>deepak.tiwari.0077@example.com</v>
       </c>
       <c r="W119" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000077&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X119" t="str">
         <v/>
@@ -10015,7 +10015,7 @@
         <v>roshni.singh.0078@example.com</v>
       </c>
       <c r="W120" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000078&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X120" t="str">
         <v/>
@@ -10095,7 +10095,7 @@
         <v>asha.iyer.0079@example.com</v>
       </c>
       <c r="W121" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000079&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X121" t="str">
         <v/>
@@ -10255,7 +10255,7 @@
         <v>vikram.bhattacharya.0081@example.com</v>
       </c>
       <c r="W123" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000081&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X123" t="str">
         <v/>
@@ -10335,7 +10335,7 @@
         <v>aarti.sharma.0082@example.com</v>
       </c>
       <c r="W124" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000082&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X124" t="str">
         <v/>
@@ -10415,7 +10415,7 @@
         <v>isha.patel.0083@example.com</v>
       </c>
       <c r="W125" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000083&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X125" t="str">
         <v/>
@@ -10495,7 +10495,7 @@
         <v>harsh.kapoor.0084@example.com</v>
       </c>
       <c r="W126" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000084&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X126" t="str">
         <v/>
@@ -10575,7 +10575,7 @@
         <v>megha.pillai.0085@example.com</v>
       </c>
       <c r="W127" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000085&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X127" t="str">
         <v/>
@@ -10655,7 +10655,7 @@
         <v>maya.sharma.0086@example.com</v>
       </c>
       <c r="W128" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000086&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X128" t="str">
         <v/>
@@ -10735,7 +10735,7 @@
         <v>swati.krishnan.0087@example.com</v>
       </c>
       <c r="W129" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000087&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X129" t="str">
         <v/>
@@ -10815,7 +10815,7 @@
         <v>anil.singh.0088@example.com</v>
       </c>
       <c r="W130" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000088&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X130" t="str">
         <v/>
@@ -10895,7 +10895,7 @@
         <v>rahul.bhandari.0089@example.com</v>
       </c>
       <c r="W131" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000089&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X131" t="str">
         <v/>
@@ -10975,7 +10975,7 @@
         <v>karan.gupta.0090@example.com</v>
       </c>
       <c r="W132" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000090&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X132" t="str">
         <v/>
@@ -11055,7 +11055,7 @@
         <v>pranav.choudhury.0091@example.com</v>
       </c>
       <c r="W133" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000091&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X133" t="str">
         <v/>
@@ -11135,7 +11135,7 @@
         <v>divya.kulkarni.0092@example.com</v>
       </c>
       <c r="W134" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000092&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X134" t="str">
         <v/>
@@ -11215,7 +11215,7 @@
         <v>sandeep.bhattacharya.0093@example.com</v>
       </c>
       <c r="W135" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000093&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X135" t="str">
         <v/>
@@ -11295,7 +11295,7 @@
         <v>manoj.choudhury.0094@example.com</v>
       </c>
       <c r="W136" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000094&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X136" t="str">
         <v/>
@@ -11375,7 +11375,7 @@
         <v>nikhil.agarwal.0095@example.com</v>
       </c>
       <c r="W137" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000095&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X137" t="str">
         <v/>
@@ -11455,7 +11455,7 @@
         <v>meena.chatterjee.0096@example.com</v>
       </c>
       <c r="W138" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000096&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X138" t="str">
         <v/>
@@ -11535,7 +11535,7 @@
         <v>anil.sharma.0097@example.com</v>
       </c>
       <c r="W139" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000097&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X139" t="str">
         <v/>
@@ -11615,7 +11615,7 @@
         <v>roshni.kapoor.0098@example.com</v>
       </c>
       <c r="W140" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000098&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X140" t="str">
         <v/>
@@ -11695,7 +11695,7 @@
         <v>shweta.gupta.0099@example.com</v>
       </c>
       <c r="W141" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-G000099&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X141" t="str">
         <v/>
@@ -11775,7 +11775,7 @@
         <v>swati.bhattacharya.0001@example.com</v>
       </c>
       <c r="W142" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000001&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X142" t="str">
         <v/>
@@ -11935,7 +11935,7 @@
         <v>meena.patel.0003@example.com</v>
       </c>
       <c r="W144" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000003&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X144" t="str">
         <v/>
@@ -12015,7 +12015,7 @@
         <v>vivek.tiwari.0004@example.com</v>
       </c>
       <c r="W145" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000004&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X145" t="str">
         <v/>
@@ -12095,7 +12095,7 @@
         <v>anjali.roy.0005@example.com</v>
       </c>
       <c r="W146" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000005&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X146" t="str">
         <v/>
@@ -12175,7 +12175,7 @@
         <v>sunita.roy.0006@example.com</v>
       </c>
       <c r="W147" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000006&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X147" t="str">
         <v/>
@@ -12255,7 +12255,7 @@
         <v>tara.mehta.0007@example.com</v>
       </c>
       <c r="W148" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000007&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X148" t="str">
         <v/>
@@ -12335,7 +12335,7 @@
         <v>geeta.mehta.0008@example.com</v>
       </c>
       <c r="W149" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000008&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X149" t="str">
         <v/>
@@ -12415,7 +12415,7 @@
         <v>megha.reddy.0009@example.com</v>
       </c>
       <c r="W150" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000009&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X150" t="str">
         <v>AMNS-V000001</v>
@@ -12495,7 +12495,7 @@
         <v>siddharth.reddy.0010@example.com</v>
       </c>
       <c r="W151" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000010&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X151" t="str">
         <v/>
@@ -12575,7 +12575,7 @@
         <v>isha.menon.0011@example.com</v>
       </c>
       <c r="W152" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000011&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X152" t="str">
         <v/>
@@ -12655,7 +12655,7 @@
         <v>manoj.das.0012@example.com</v>
       </c>
       <c r="W153" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000012&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X153" t="str">
         <v/>
@@ -12735,7 +12735,7 @@
         <v>anjali.das.0013@example.com</v>
       </c>
       <c r="W154" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000013&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X154" t="str">
         <v/>
@@ -12815,7 +12815,7 @@
         <v>varun.pillai.0014@example.com</v>
       </c>
       <c r="W155" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000014&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X155" t="str">
         <v/>
@@ -12895,7 +12895,7 @@
         <v>swati.joshi.0015@example.com</v>
       </c>
       <c r="W156" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000015&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X156" t="str">
         <v/>
@@ -12975,7 +12975,7 @@
         <v>ritu.gupta.0016@example.com</v>
       </c>
       <c r="W157" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000016&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X157" t="str">
         <v/>
@@ -13055,7 +13055,7 @@
         <v>ritu.chatterjee.0017@example.com</v>
       </c>
       <c r="W158" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000017&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X158" t="str">
         <v/>
@@ -13135,7 +13135,7 @@
         <v>priya.gupta.0018@example.com</v>
       </c>
       <c r="W159" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000018&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X159" t="str">
         <v/>
@@ -13215,7 +13215,7 @@
         <v>anjali.agarwal.0019@example.com</v>
       </c>
       <c r="W160" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000019&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X160" t="str">
         <v/>
@@ -13295,7 +13295,7 @@
         <v>meena.kulkarni.0020@example.com</v>
       </c>
       <c r="W161" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000020&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X161" t="str">
         <v/>
@@ -13375,7 +13375,7 @@
         <v>ritu.verma.0021@example.com</v>
       </c>
       <c r="W162" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000021&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X162" t="str">
         <v/>
@@ -13455,7 +13455,7 @@
         <v>aman.kulkarni.0022@example.com</v>
       </c>
       <c r="W163" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000022&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X163" t="str">
         <v/>
@@ -13535,7 +13535,7 @@
         <v>ritu.bhattacharya.0023@example.com</v>
       </c>
       <c r="W164" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000023&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X164" t="str">
         <v/>
@@ -13615,7 +13615,7 @@
         <v>kavya.pillai.0024@example.com</v>
       </c>
       <c r="W165" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000024&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X165" t="str">
         <v/>
@@ -13695,7 +13695,7 @@
         <v>roshni.reddy.0025@example.com</v>
       </c>
       <c r="W166" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000025&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X166" t="str">
         <v/>
@@ -13855,7 +13855,7 @@
         <v>akash.bhandari.0027@example.com</v>
       </c>
       <c r="W168" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000027&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X168" t="str">
         <v/>
@@ -13935,7 +13935,7 @@
         <v>lakshmi.bhatt.0028@example.com</v>
       </c>
       <c r="W169" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000028&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X169" t="str">
         <v/>
@@ -14015,7 +14015,7 @@
         <v>sandeep.bhatt.0029@example.com</v>
       </c>
       <c r="W170" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000029&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X170" t="str">
         <v>AMNS-V000001</v>
@@ -14095,7 +14095,7 @@
         <v>pooja.iyer.0030@example.com</v>
       </c>
       <c r="W171" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000030&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X171" t="str">
         <v/>
@@ -14175,7 +14175,7 @@
         <v>divya.menon.0031@example.com</v>
       </c>
       <c r="W172" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000031&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X172" t="str">
         <v/>
@@ -14255,7 +14255,7 @@
         <v>tara.saxena.0032@example.com</v>
       </c>
       <c r="W173" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000032&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X173" t="str">
         <v/>
@@ -14335,7 +14335,7 @@
         <v>rohit.agarwal.0033@example.com</v>
       </c>
       <c r="W174" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000033&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X174" t="str">
         <v/>
@@ -14415,7 +14415,7 @@
         <v>aman.banerjee.0034@example.com</v>
       </c>
       <c r="W175" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000034&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X175" t="str">
         <v/>
@@ -14495,7 +14495,7 @@
         <v>deepak.iyer.0035@example.com</v>
       </c>
       <c r="W176" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000035&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X176" t="str">
         <v/>
@@ -14575,7 +14575,7 @@
         <v>neha.saxena.0036@example.com</v>
       </c>
       <c r="W177" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000036&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X177" t="str">
         <v/>
@@ -14655,7 +14655,7 @@
         <v>aman.bhandari.0037@example.com</v>
       </c>
       <c r="W178" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000037&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X178" t="str">
         <v>AMNS-V000001</v>
@@ -14735,7 +14735,7 @@
         <v>deepak.krishnan.0038@example.com</v>
       </c>
       <c r="W179" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000038&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X179" t="str">
         <v/>
@@ -14815,7 +14815,7 @@
         <v>ramesh.kulkarni.0039@example.com</v>
       </c>
       <c r="W180" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000039&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X180" t="str">
         <v/>
@@ -14895,7 +14895,7 @@
         <v>sanjay.kapoor.0040@example.com</v>
       </c>
       <c r="W181" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000040&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X181" t="str">
         <v/>
@@ -14975,7 +14975,7 @@
         <v>kavya.reddy.0041@example.com</v>
       </c>
       <c r="W182" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000041&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X182" t="str">
         <v/>
@@ -15055,7 +15055,7 @@
         <v>rohit.iyer.0042@example.com</v>
       </c>
       <c r="W183" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000042&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X183" t="str">
         <v/>
@@ -15135,7 +15135,7 @@
         <v>aarti.sharma.0043@example.com</v>
       </c>
       <c r="W184" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000043&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X184" t="str">
         <v/>
@@ -15215,7 +15215,7 @@
         <v>harsh.menon.0044@example.com</v>
       </c>
       <c r="W185" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000044&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X185" t="str">
         <v/>
@@ -15295,7 +15295,7 @@
         <v>suresh.singh.0045@example.com</v>
       </c>
       <c r="W186" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000045&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X186" t="str">
         <v/>
@@ -15375,7 +15375,7 @@
         <v>vivek.sharma.0046@example.com</v>
       </c>
       <c r="W187" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000046&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X187" t="str">
         <v/>
@@ -15455,7 +15455,7 @@
         <v>anil.roy.0047@example.com</v>
       </c>
       <c r="W188" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000047&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X188" t="str">
         <v/>
@@ -15535,7 +15535,7 @@
         <v>madhuri.pillai.0048@example.com</v>
       </c>
       <c r="W189" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000048&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X189" t="str">
         <v/>
@@ -15615,7 +15615,7 @@
         <v>divya.iyer.0049@example.com</v>
       </c>
       <c r="W190" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000049&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X190" t="str">
         <v>AMNS-V000001</v>
@@ -15695,7 +15695,7 @@
         <v>tara.kapoor.0050@example.com</v>
       </c>
       <c r="W191" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000050&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X191" t="str">
         <v/>
@@ -15775,7 +15775,7 @@
         <v>vivek.sharma.0051@example.com</v>
       </c>
       <c r="W192" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000051&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X192" t="str">
         <v/>
@@ -15855,7 +15855,7 @@
         <v>divya.singh.0052@example.com</v>
       </c>
       <c r="W193" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000052&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X193" t="str">
         <v/>
@@ -15935,7 +15935,7 @@
         <v>neha.patel.0053@example.com</v>
       </c>
       <c r="W194" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000053&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X194" t="str">
         <v/>
@@ -16015,7 +16015,7 @@
         <v>karan.nair.0054@example.com</v>
       </c>
       <c r="W195" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000054&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X195" t="str">
         <v/>
@@ -16095,7 +16095,7 @@
         <v>kirti.agarwal.0055@example.com</v>
       </c>
       <c r="W196" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000055&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X196" t="str">
         <v/>
@@ -16175,7 +16175,7 @@
         <v>sneha.tiwari.0056@example.com</v>
       </c>
       <c r="W197" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000056&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X197" t="str">
         <v/>
@@ -16255,7 +16255,7 @@
         <v>arjun.das.0057@example.com</v>
       </c>
       <c r="W198" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000057&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X198" t="str">
         <v/>
@@ -16335,7 +16335,7 @@
         <v>rohit.nair.0058@example.com</v>
       </c>
       <c r="W199" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000058&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X199" t="str">
         <v/>
@@ -16415,7 +16415,7 @@
         <v>karan.sharma.0059@example.com</v>
       </c>
       <c r="W200" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000059&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X200" t="str">
         <v/>
@@ -16495,7 +16495,7 @@
         <v>kirti.mehta.0060@example.com</v>
       </c>
       <c r="W201" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000060&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X201" t="str">
         <v/>
@@ -16575,7 +16575,7 @@
         <v>aman.tiwari.0061@example.com</v>
       </c>
       <c r="W202" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000061&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X202" t="str">
         <v/>
@@ -16655,7 +16655,7 @@
         <v>aman.mehta.0062@example.com</v>
       </c>
       <c r="W203" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000062&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X203" t="str">
         <v/>
@@ -16815,7 +16815,7 @@
         <v>roshni.kulkarni.0064@example.com</v>
       </c>
       <c r="W205" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000064&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X205" t="str">
         <v/>
@@ -16895,7 +16895,7 @@
         <v>sunita.menon.0065@example.com</v>
       </c>
       <c r="W206" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000065&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X206" t="str">
         <v/>
@@ -17055,7 +17055,7 @@
         <v>ananya.chatterjee.0067@example.com</v>
       </c>
       <c r="W208" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000067&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X208" t="str">
         <v/>
@@ -17135,7 +17135,7 @@
         <v>varun.pillai.0068@example.com</v>
       </c>
       <c r="W209" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000068&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X209" t="str">
         <v/>
@@ -17215,7 +17215,7 @@
         <v>manoj.tiwari.0069@example.com</v>
       </c>
       <c r="W210" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000069&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X210" t="str">
         <v/>
@@ -17295,7 +17295,7 @@
         <v>pallavi.kapoor.0070@example.com</v>
       </c>
       <c r="W211" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000070&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X211" t="str">
         <v/>
@@ -17375,7 +17375,7 @@
         <v>vikram.krishnan.0071@example.com</v>
       </c>
       <c r="W212" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000071&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X212" t="str">
         <v/>
@@ -17455,7 +17455,7 @@
         <v>vivek.trivedi.0072@example.com</v>
       </c>
       <c r="W213" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000072&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X213" t="str">
         <v/>
@@ -17535,7 +17535,7 @@
         <v>kirti.reddy.0073@example.com</v>
       </c>
       <c r="W214" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000073&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X214" t="str">
         <v/>
@@ -17615,7 +17615,7 @@
         <v>maya.verma.0074@example.com</v>
       </c>
       <c r="W215" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000074&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X215" t="str">
         <v/>
@@ -17935,7 +17935,7 @@
         <v>rahul.krishnan.0078@example.com</v>
       </c>
       <c r="W219" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000078&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X219" t="str">
         <v/>
@@ -18095,7 +18095,7 @@
         <v>isha.agarwal.0080@example.com</v>
       </c>
       <c r="W221" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000080&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X221" t="str">
         <v/>
@@ -18175,7 +18175,7 @@
         <v>anil.bhattacharya.0081@example.com</v>
       </c>
       <c r="W222" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000081&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X222" t="str">
         <v/>
@@ -18335,7 +18335,7 @@
         <v>vivek.joshi.0083@example.com</v>
       </c>
       <c r="W224" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000083&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X224" t="str">
         <v/>
@@ -18415,7 +18415,7 @@
         <v>kavya.mehta.0084@example.com</v>
       </c>
       <c r="W225" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000084&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X225" t="str">
         <v/>
@@ -18495,7 +18495,7 @@
         <v>pallavi.sharma.0085@example.com</v>
       </c>
       <c r="W226" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000085&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X226" t="str">
         <v/>
@@ -18575,7 +18575,7 @@
         <v>anjali.joshi.0086@example.com</v>
       </c>
       <c r="W227" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000086&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X227" t="str">
         <v/>
@@ -18655,7 +18655,7 @@
         <v>vivek.bhatt.0087@example.com</v>
       </c>
       <c r="W228" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000087&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X228" t="str">
         <v/>
@@ -18735,7 +18735,7 @@
         <v>vivek.nair.0088@example.com</v>
       </c>
       <c r="W229" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000088&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X229" t="str">
         <v/>
@@ -18815,7 +18815,7 @@
         <v>maya.pillai.0089@example.com</v>
       </c>
       <c r="W230" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000089&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X230" t="str">
         <v/>
@@ -18895,7 +18895,7 @@
         <v>aarti.kulkarni.0090@example.com</v>
       </c>
       <c r="W231" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000090&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X231" t="str">
         <v/>
@@ -18975,7 +18975,7 @@
         <v>nikhil.krishnan.0091@example.com</v>
       </c>
       <c r="W232" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000091&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X232" t="str">
         <v/>
@@ -19055,7 +19055,7 @@
         <v>aditya.joshi.0092@example.com</v>
       </c>
       <c r="W233" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000092&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X233" t="str">
         <v/>
@@ -19135,7 +19135,7 @@
         <v>riya.patel.0093@example.com</v>
       </c>
       <c r="W234" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000093&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X234" t="str">
         <v/>
@@ -19215,7 +19215,7 @@
         <v>sandeep.saxena.0094@example.com</v>
       </c>
       <c r="W235" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000094&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X235" t="str">
         <v>AMNS-V000001</v>
@@ -19295,7 +19295,7 @@
         <v>tara.chatterjee.0095@example.com</v>
       </c>
       <c r="W236" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000095&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X236" t="str">
         <v/>
@@ -19375,7 +19375,7 @@
         <v>rahul.bhandari.0096@example.com</v>
       </c>
       <c r="W237" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000096&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X237" t="str">
         <v/>
@@ -19455,7 +19455,7 @@
         <v>vikram.trivedi.0097@example.com</v>
       </c>
       <c r="W238" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000097&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X238" t="str">
         <v/>
@@ -19535,7 +19535,7 @@
         <v>divya.nair.0098@example.com</v>
       </c>
       <c r="W239" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000098&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X239" t="str">
         <v/>
@@ -19615,7 +19615,7 @@
         <v>lakshmi.chatterjee.0099@example.com</v>
       </c>
       <c r="W240" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000099&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X240" t="str">
         <v/>
@@ -19695,7 +19695,7 @@
         <v>sunita.sharma.0100@example.com</v>
       </c>
       <c r="W241" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000100&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X241" t="str">
         <v/>
@@ -19775,7 +19775,7 @@
         <v>ramesh.nair.0101@example.com</v>
       </c>
       <c r="W242" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000101&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X242" t="str">
         <v/>
@@ -19855,7 +19855,7 @@
         <v>tara.menon.0102@example.com</v>
       </c>
       <c r="W243" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000102&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X243" t="str">
         <v/>
@@ -19935,7 +19935,7 @@
         <v>pranav.iyer.0103@example.com</v>
       </c>
       <c r="W244" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000103&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X244" t="str">
         <v>AMNS-V000001</v>
@@ -20015,7 +20015,7 @@
         <v>shweta.banerjee.0104@example.com</v>
       </c>
       <c r="W245" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000104&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X245" t="str">
         <v/>
@@ -20095,7 +20095,7 @@
         <v>swati.nair.0105@example.com</v>
       </c>
       <c r="W246" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000105&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X246" t="str">
         <v/>
@@ -20175,7 +20175,7 @@
         <v>anil.mukherjee.0106@example.com</v>
       </c>
       <c r="W247" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000106&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X247" t="str">
         <v/>
@@ -20255,7 +20255,7 @@
         <v>sandeep.gupta.0107@example.com</v>
       </c>
       <c r="W248" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000107&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X248" t="str">
         <v>AMNS-V000001</v>
@@ -20335,7 +20335,7 @@
         <v>yash.singh.0108@example.com</v>
       </c>
       <c r="W249" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000108&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X249" t="str">
         <v/>
@@ -20415,7 +20415,7 @@
         <v>manoj.joshi.0109@example.com</v>
       </c>
       <c r="W250" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000109&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X250" t="str">
         <v/>
@@ -20495,7 +20495,7 @@
         <v>neha.sharma.0110@example.com</v>
       </c>
       <c r="W251" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000110&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X251" t="str">
         <v/>
@@ -20575,7 +20575,7 @@
         <v>lakshmi.malhotra.0111@example.com</v>
       </c>
       <c r="W252" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000111&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X252" t="str">
         <v/>
@@ -20655,7 +20655,7 @@
         <v>megha.das.0112@example.com</v>
       </c>
       <c r="W253" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000112&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X253" t="str">
         <v/>
@@ -20735,7 +20735,7 @@
         <v>swati.sharma.0113@example.com</v>
       </c>
       <c r="W254" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000113&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X254" t="str">
         <v/>
@@ -20815,7 +20815,7 @@
         <v>shweta.bhatt.0114@example.com</v>
       </c>
       <c r="W255" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000114&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X255" t="str">
         <v>AMNS-V000001</v>
@@ -20975,7 +20975,7 @@
         <v>meena.bhatt.0116@example.com</v>
       </c>
       <c r="W257" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000116&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X257" t="str">
         <v/>
@@ -21055,7 +21055,7 @@
         <v>pranav.krishnan.0117@example.com</v>
       </c>
       <c r="W258" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000117&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X258" t="str">
         <v/>
@@ -21135,7 +21135,7 @@
         <v>varun.gupta.0118@example.com</v>
       </c>
       <c r="W259" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000118&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X259" t="str">
         <v/>
@@ -21215,7 +21215,7 @@
         <v>lakshmi.das.0119@example.com</v>
       </c>
       <c r="W260" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000119&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X260" t="str">
         <v/>
@@ -21295,7 +21295,7 @@
         <v>kunal.roy.0120@example.com</v>
       </c>
       <c r="W261" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000120&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X261" t="str">
         <v/>
@@ -21375,7 +21375,7 @@
         <v>meena.iyer.0121@example.com</v>
       </c>
       <c r="W262" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000121&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X262" t="str">
         <v/>
@@ -21455,7 +21455,7 @@
         <v>varun.choudhury.0122@example.com</v>
       </c>
       <c r="W263" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000122&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X263" t="str">
         <v>AMNS-V000001</v>
@@ -21535,7 +21535,7 @@
         <v>maya.banerjee.0123@example.com</v>
       </c>
       <c r="W264" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000123&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X264" t="str">
         <v/>
@@ -21615,7 +21615,7 @@
         <v>swati.mehta.0124@example.com</v>
       </c>
       <c r="W265" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000124&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X265" t="str">
         <v/>
@@ -21695,7 +21695,7 @@
         <v>meena.agarwal.0125@example.com</v>
       </c>
       <c r="W266" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000125&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X266" t="str">
         <v/>
@@ -21775,7 +21775,7 @@
         <v>meena.bhattacharya.0126@example.com</v>
       </c>
       <c r="W267" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000126&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X267" t="str">
         <v/>
@@ -21855,7 +21855,7 @@
         <v>sunita.tiwari.0127@example.com</v>
       </c>
       <c r="W268" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000127&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X268" t="str">
         <v/>
@@ -21935,7 +21935,7 @@
         <v>aarti.sharma.0128@example.com</v>
       </c>
       <c r="W269" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000128&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X269" t="str">
         <v/>
@@ -22015,7 +22015,7 @@
         <v>manoj.trivedi.0129@example.com</v>
       </c>
       <c r="W270" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000129&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X270" t="str">
         <v/>
@@ -22095,7 +22095,7 @@
         <v>harsh.kapoor.0130@example.com</v>
       </c>
       <c r="W271" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000130&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X271" t="str">
         <v/>
@@ -22175,7 +22175,7 @@
         <v>neha.krishnan.0131@example.com</v>
       </c>
       <c r="W272" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000131&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X272" t="str">
         <v/>
@@ -22255,7 +22255,7 @@
         <v>deepak.verma.0132@example.com</v>
       </c>
       <c r="W273" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000132&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X273" t="str">
         <v/>
@@ -22415,7 +22415,7 @@
         <v>isha.joshi.0134@example.com</v>
       </c>
       <c r="W275" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000134&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X275" t="str">
         <v/>
@@ -22495,7 +22495,7 @@
         <v>priya.roy.0135@example.com</v>
       </c>
       <c r="W276" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000135&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X276" t="str">
         <v/>
@@ -22575,7 +22575,7 @@
         <v>siddharth.saxena.0136@example.com</v>
       </c>
       <c r="W277" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000136&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X277" t="str">
         <v/>
@@ -22655,7 +22655,7 @@
         <v>rahul.reddy.0137@example.com</v>
       </c>
       <c r="W278" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000137&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X278" t="str">
         <v>AMNS-V000001</v>
@@ -22815,7 +22815,7 @@
         <v>sanjay.singh.0139@example.com</v>
       </c>
       <c r="W280" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000139&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X280" t="str">
         <v/>
@@ -22895,7 +22895,7 @@
         <v>aarti.menon.0140@example.com</v>
       </c>
       <c r="W281" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000140&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X281" t="str">
         <v/>
@@ -22975,7 +22975,7 @@
         <v>harsh.saxena.0141@example.com</v>
       </c>
       <c r="W282" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000141&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X282" t="str">
         <v/>
@@ -23135,7 +23135,7 @@
         <v>varun.mukherjee.0143@example.com</v>
       </c>
       <c r="W284" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000143&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X284" t="str">
         <v/>
@@ -23215,7 +23215,7 @@
         <v>aditya.gupta.0144@example.com</v>
       </c>
       <c r="W285" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000144&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X285" t="str">
         <v/>
@@ -23295,7 +23295,7 @@
         <v>tara.kulkarni.0145@example.com</v>
       </c>
       <c r="W286" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000145&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X286" t="str">
         <v/>
@@ -23375,7 +23375,7 @@
         <v>aarti.singh.0146@example.com</v>
       </c>
       <c r="W287" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000146&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X287" t="str">
         <v/>
@@ -23455,7 +23455,7 @@
         <v>vikram.sharma.0147@example.com</v>
       </c>
       <c r="W288" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000147&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X288" t="str">
         <v/>
@@ -23535,7 +23535,7 @@
         <v>karan.das.0148@example.com</v>
       </c>
       <c r="W289" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000148&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X289" t="str">
         <v/>
@@ -23615,7 +23615,7 @@
         <v>swati.choudhury.0149@example.com</v>
       </c>
       <c r="W290" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000149&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X290" t="str">
         <v>AMNS-V000001</v>
@@ -23695,7 +23695,7 @@
         <v>swati.trivedi.0150@example.com</v>
       </c>
       <c r="W291" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000150&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X291" t="str">
         <v/>
@@ -23775,7 +23775,7 @@
         <v>ritu.kulkarni.0151@example.com</v>
       </c>
       <c r="W292" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000151&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X292" t="str">
         <v/>
@@ -23855,7 +23855,7 @@
         <v>akash.das.0152@example.com</v>
       </c>
       <c r="W293" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000152&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X293" t="str">
         <v/>
@@ -23935,7 +23935,7 @@
         <v>anil.pillai.0153@example.com</v>
       </c>
       <c r="W294" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000153&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X294" t="str">
         <v/>
@@ -24015,7 +24015,7 @@
         <v>aman.joshi.0154@example.com</v>
       </c>
       <c r="W295" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000154&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X295" t="str">
         <v/>
@@ -24095,7 +24095,7 @@
         <v>sunita.tiwari.0155@example.com</v>
       </c>
       <c r="W296" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000155&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X296" t="str">
         <v/>
@@ -24255,7 +24255,7 @@
         <v>sunita.nair.0157@example.com</v>
       </c>
       <c r="W298" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000157&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X298" t="str">
         <v/>
@@ -24335,7 +24335,7 @@
         <v>sandeep.verma.0158@example.com</v>
       </c>
       <c r="W299" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000158&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X299" t="str">
         <v/>
@@ -24415,7 +24415,7 @@
         <v>riya.bhandari.0159@example.com</v>
       </c>
       <c r="W300" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000159&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X300" t="str">
         <v/>
@@ -24495,7 +24495,7 @@
         <v>aditya.tiwari.0160@example.com</v>
       </c>
       <c r="W301" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000160&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X301" t="str">
         <v/>
@@ -24655,7 +24655,7 @@
         <v>siddharth.saxena.0162@example.com</v>
       </c>
       <c r="W303" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000162&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X303" t="str">
         <v/>
@@ -24735,7 +24735,7 @@
         <v>yash.bhandari.0163@example.com</v>
       </c>
       <c r="W304" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000163&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X304" t="str">
         <v/>
@@ -24815,7 +24815,7 @@
         <v>siddharth.gupta.0164@example.com</v>
       </c>
       <c r="W305" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000164&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X305" t="str">
         <v/>
@@ -24895,7 +24895,7 @@
         <v>aman.tiwari.0165@example.com</v>
       </c>
       <c r="W306" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000165&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X306" t="str">
         <v/>
@@ -24975,7 +24975,7 @@
         <v>siddharth.kulkarni.0166@example.com</v>
       </c>
       <c r="W307" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000166&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X307" t="str">
         <v/>
@@ -25055,7 +25055,7 @@
         <v>megha.chatterjee.0167@example.com</v>
       </c>
       <c r="W308" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000167&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X308" t="str">
         <v/>
@@ -25135,7 +25135,7 @@
         <v>yash.chatterjee.0168@example.com</v>
       </c>
       <c r="W309" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000168&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X309" t="str">
         <v/>
@@ -25215,7 +25215,7 @@
         <v>rahul.tiwari.0169@example.com</v>
       </c>
       <c r="W310" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000169&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X310" t="str">
         <v/>
@@ -25295,7 +25295,7 @@
         <v>ramesh.nair.0170@example.com</v>
       </c>
       <c r="W311" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000170&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X311" t="str">
         <v/>
@@ -25375,7 +25375,7 @@
         <v>vivek.bhatt.0171@example.com</v>
       </c>
       <c r="W312" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000171&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X312" t="str">
         <v>AMNS-V000001</v>
@@ -25455,7 +25455,7 @@
         <v>deepak.joshi.0172@example.com</v>
       </c>
       <c r="W313" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000172&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X313" t="str">
         <v/>
@@ -25535,7 +25535,7 @@
         <v>ramesh.nair.0173@example.com</v>
       </c>
       <c r="W314" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000173&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X314" t="str">
         <v/>
@@ -25615,7 +25615,7 @@
         <v>varun.tiwari.0174@example.com</v>
       </c>
       <c r="W315" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000174&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X315" t="str">
         <v/>
@@ -25695,7 +25695,7 @@
         <v>neha.singh.0175@example.com</v>
       </c>
       <c r="W316" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000175&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X316" t="str">
         <v/>
@@ -25775,7 +25775,7 @@
         <v>vivek.iyer.0176@example.com</v>
       </c>
       <c r="W317" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000176&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X317" t="str">
         <v>AMNS-V000001</v>
@@ -25855,7 +25855,7 @@
         <v>megha.joshi.0177@example.com</v>
       </c>
       <c r="W318" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000177&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X318" t="str">
         <v/>
@@ -25935,7 +25935,7 @@
         <v>roshni.banerjee.0178@example.com</v>
       </c>
       <c r="W319" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000178&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X319" t="str">
         <v/>
@@ -26015,7 +26015,7 @@
         <v>megha.das.0179@example.com</v>
       </c>
       <c r="W320" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000179&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X320" t="str">
         <v/>
@@ -26095,7 +26095,7 @@
         <v>nikhil.agarwal.0180@example.com</v>
       </c>
       <c r="W321" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000180&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X321" t="str">
         <v>AMNS-V000001</v>
@@ -26175,7 +26175,7 @@
         <v>suresh.malhotra.0181@example.com</v>
       </c>
       <c r="W322" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000181&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X322" t="str">
         <v/>
@@ -26255,7 +26255,7 @@
         <v>anil.joshi.0182@example.com</v>
       </c>
       <c r="W323" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000182&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X323" t="str">
         <v/>
@@ -26335,7 +26335,7 @@
         <v>madhuri.banerjee.0183@example.com</v>
       </c>
       <c r="W324" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000183&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X324" t="str">
         <v/>
@@ -26415,7 +26415,7 @@
         <v>rohit.sharma.0184@example.com</v>
       </c>
       <c r="W325" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000184&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X325" t="str">
         <v/>
@@ -26495,7 +26495,7 @@
         <v>priya.patel.0185@example.com</v>
       </c>
       <c r="W326" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000185&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X326" t="str">
         <v/>
@@ -26575,7 +26575,7 @@
         <v>anil.desai.0186@example.com</v>
       </c>
       <c r="W327" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000186&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X327" t="str">
         <v/>
@@ -26655,7 +26655,7 @@
         <v>lakshmi.chatterjee.0187@example.com</v>
       </c>
       <c r="W328" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000187&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X328" t="str">
         <v/>
@@ -26735,7 +26735,7 @@
         <v>harsh.gupta.0188@example.com</v>
       </c>
       <c r="W329" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000188&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X329" t="str">
         <v/>
@@ -26815,7 +26815,7 @@
         <v>siddharth.tiwari.0189@example.com</v>
       </c>
       <c r="W330" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000189&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X330" t="str">
         <v>AMNS-V000001</v>
@@ -26895,7 +26895,7 @@
         <v>ramesh.mukherjee.0190@example.com</v>
       </c>
       <c r="W331" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000190&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X331" t="str">
         <v/>
@@ -26975,7 +26975,7 @@
         <v>swati.menon.0191@example.com</v>
       </c>
       <c r="W332" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000191&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X332" t="str">
         <v/>
@@ -27055,7 +27055,7 @@
         <v>swati.krishnan.0192@example.com</v>
       </c>
       <c r="W333" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000192&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X333" t="str">
         <v/>
@@ -27135,7 +27135,7 @@
         <v>ananya.bhandari.0193@example.com</v>
       </c>
       <c r="W334" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000193&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X334" t="str">
         <v/>
@@ -27215,7 +27215,7 @@
         <v>lakshmi.malhotra.0194@example.com</v>
       </c>
       <c r="W335" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000194&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X335" t="str">
         <v/>
@@ -27295,7 +27295,7 @@
         <v>karan.singh.0195@example.com</v>
       </c>
       <c r="W336" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000195&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X336" t="str">
         <v/>
@@ -27375,7 +27375,7 @@
         <v>anil.joshi.0196@example.com</v>
       </c>
       <c r="W337" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000196&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X337" t="str">
         <v>AMNS-V000001</v>
@@ -27455,7 +27455,7 @@
         <v>shweta.sharma.0197@example.com</v>
       </c>
       <c r="W338" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000197&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X338" t="str">
         <v/>
@@ -27535,7 +27535,7 @@
         <v>deepak.verma.0198@example.com</v>
       </c>
       <c r="W339" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000198&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X339" t="str">
         <v/>
@@ -27615,7 +27615,7 @@
         <v>karan.iyer.0199@example.com</v>
       </c>
       <c r="W340" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000199&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X340" t="str">
         <v/>
@@ -27695,7 +27695,7 @@
         <v>kunal.tiwari.0200@example.com</v>
       </c>
       <c r="W341" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000200&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X341" t="str">
         <v/>
@@ -27775,7 +27775,7 @@
         <v>rahul.menon.0201@example.com</v>
       </c>
       <c r="W342" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000201&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X342" t="str">
         <v/>
@@ -27855,7 +27855,7 @@
         <v>pallavi.bhatt.0202@example.com</v>
       </c>
       <c r="W343" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000202&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X343" t="str">
         <v>AMNS-V000001</v>
@@ -27935,7 +27935,7 @@
         <v>yash.singh.0203@example.com</v>
       </c>
       <c r="W344" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000203&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X344" t="str">
         <v/>
@@ -28015,7 +28015,7 @@
         <v>maya.tiwari.0204@example.com</v>
       </c>
       <c r="W345" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000204&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X345" t="str">
         <v>AMNS-V000001</v>
@@ -28095,7 +28095,7 @@
         <v>madhuri.gupta.0205@example.com</v>
       </c>
       <c r="W346" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000205&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X346" t="str">
         <v/>
@@ -28175,7 +28175,7 @@
         <v>madhuri.patel.0206@example.com</v>
       </c>
       <c r="W347" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000206&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X347" t="str">
         <v/>
@@ -28335,7 +28335,7 @@
         <v>geeta.mehta.0208@example.com</v>
       </c>
       <c r="W349" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000208&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X349" t="str">
         <v/>
@@ -28415,7 +28415,7 @@
         <v>karan.roy.0209@example.com</v>
       </c>
       <c r="W350" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000209&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X350" t="str">
         <v/>
@@ -28495,7 +28495,7 @@
         <v>nikhil.trivedi.0210@example.com</v>
       </c>
       <c r="W351" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000210&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X351" t="str">
         <v>AMNS-V000001</v>
@@ -28575,7 +28575,7 @@
         <v>tanmay.joshi.0211@example.com</v>
       </c>
       <c r="W352" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000211&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X352" t="str">
         <v/>
@@ -28655,7 +28655,7 @@
         <v>riya.verma.0212@example.com</v>
       </c>
       <c r="W353" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000212&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X353" t="str">
         <v/>
@@ -28735,7 +28735,7 @@
         <v>madhuri.agarwal.0213@example.com</v>
       </c>
       <c r="W354" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000213&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X354" t="str">
         <v/>
@@ -28815,7 +28815,7 @@
         <v>suresh.krishnan.0214@example.com</v>
       </c>
       <c r="W355" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000214&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X355" t="str">
         <v/>
@@ -28895,7 +28895,7 @@
         <v>kunal.sharma.0215@example.com</v>
       </c>
       <c r="W356" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000215&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X356" t="str">
         <v/>
@@ -28975,7 +28975,7 @@
         <v>roshni.mehta.0216@example.com</v>
       </c>
       <c r="W357" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000216&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X357" t="str">
         <v/>
@@ -29135,7 +29135,7 @@
         <v>lakshmi.menon.0218@example.com</v>
       </c>
       <c r="W359" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000218&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X359" t="str">
         <v/>
@@ -29215,7 +29215,7 @@
         <v>manoj.desai.0219@example.com</v>
       </c>
       <c r="W360" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000219&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X360" t="str">
         <v/>
@@ -29375,7 +29375,7 @@
         <v>rohit.kulkarni.0221@example.com</v>
       </c>
       <c r="W362" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000221&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X362" t="str">
         <v/>
@@ -29455,7 +29455,7 @@
         <v>sanjay.krishnan.0222@example.com</v>
       </c>
       <c r="W363" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000222&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X363" t="str">
         <v/>
@@ -29535,7 +29535,7 @@
         <v>riya.kulkarni.0223@example.com</v>
       </c>
       <c r="W364" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000223&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X364" t="str">
         <v/>
@@ -29615,7 +29615,7 @@
         <v>ananya.menon.0224@example.com</v>
       </c>
       <c r="W365" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000224&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X365" t="str">
         <v/>
@@ -29695,7 +29695,7 @@
         <v>kirti.kulkarni.0225@example.com</v>
       </c>
       <c r="W366" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000225&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X366" t="str">
         <v/>
@@ -29775,7 +29775,7 @@
         <v>kirti.chatterjee.0226@example.com</v>
       </c>
       <c r="W367" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000226&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X367" t="str">
         <v/>
@@ -29855,7 +29855,7 @@
         <v>sunita.reddy.0227@example.com</v>
       </c>
       <c r="W368" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000227&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X368" t="str">
         <v/>
@@ -29935,7 +29935,7 @@
         <v>nikhil.verma.0228@example.com</v>
       </c>
       <c r="W369" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000228&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X369" t="str">
         <v/>
@@ -30015,7 +30015,7 @@
         <v>pranav.singh.0229@example.com</v>
       </c>
       <c r="W370" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000229&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X370" t="str">
         <v/>
@@ -30095,7 +30095,7 @@
         <v>kunal.trivedi.0230@example.com</v>
       </c>
       <c r="W371" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000230&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X371" t="str">
         <v/>
@@ -30175,7 +30175,7 @@
         <v>lakshmi.gupta.0231@example.com</v>
       </c>
       <c r="W372" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000231&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X372" t="str">
         <v/>
@@ -30255,7 +30255,7 @@
         <v>roshni.bhatt.0232@example.com</v>
       </c>
       <c r="W373" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000232&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X373" t="str">
         <v/>
@@ -30335,7 +30335,7 @@
         <v>vikram.patel.0233@example.com</v>
       </c>
       <c r="W374" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000233&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X374" t="str">
         <v/>
@@ -30495,7 +30495,7 @@
         <v>ramesh.saxena.0235@example.com</v>
       </c>
       <c r="W376" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000235&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X376" t="str">
         <v/>
@@ -30575,7 +30575,7 @@
         <v>kavya.singh.0236@example.com</v>
       </c>
       <c r="W377" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000236&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X377" t="str">
         <v/>
@@ -30655,7 +30655,7 @@
         <v>vivek.mehta.0237@example.com</v>
       </c>
       <c r="W378" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000237&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X378" t="str">
         <v/>
@@ -30735,7 +30735,7 @@
         <v>rohit.roy.0238@example.com</v>
       </c>
       <c r="W379" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000238&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X379" t="str">
         <v/>
@@ -30815,7 +30815,7 @@
         <v>anjali.nair.0239@example.com</v>
       </c>
       <c r="W380" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000239&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X380" t="str">
         <v/>
@@ -30895,7 +30895,7 @@
         <v>aditya.agarwal.0240@example.com</v>
       </c>
       <c r="W381" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000240&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X381" t="str">
         <v/>
@@ -30975,7 +30975,7 @@
         <v>kunal.bhattacharya.0241@example.com</v>
       </c>
       <c r="W382" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000241&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X382" t="str">
         <v/>
@@ -31055,7 +31055,7 @@
         <v>geeta.mehta.0242@example.com</v>
       </c>
       <c r="W383" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000242&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X383" t="str">
         <v/>
@@ -31135,7 +31135,7 @@
         <v>rahul.menon.0243@example.com</v>
       </c>
       <c r="W384" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000243&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X384" t="str">
         <v/>
@@ -31215,7 +31215,7 @@
         <v>asha.reddy.0244@example.com</v>
       </c>
       <c r="W385" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000244&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X385" t="str">
         <v>AMNS-V000001</v>
@@ -31295,7 +31295,7 @@
         <v>harsh.roy.0245@example.com</v>
       </c>
       <c r="W386" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000245&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X386" t="str">
         <v/>
@@ -31375,7 +31375,7 @@
         <v>sneha.banerjee.0246@example.com</v>
       </c>
       <c r="W387" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000246&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X387" t="str">
         <v/>
@@ -31455,7 +31455,7 @@
         <v>ritu.reddy.0247@example.com</v>
       </c>
       <c r="W388" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000247&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X388" t="str">
         <v/>
@@ -31535,7 +31535,7 @@
         <v>sunita.mukherjee.0248@example.com</v>
       </c>
       <c r="W389" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000248&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X389" t="str">
         <v/>
@@ -31615,7 +31615,7 @@
         <v>sandeep.singh.0249@example.com</v>
       </c>
       <c r="W390" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000249&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X390" t="str">
         <v/>
@@ -31695,7 +31695,7 @@
         <v>lakshmi.singh.0250@example.com</v>
       </c>
       <c r="W391" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-M000250&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X391" t="str">
         <v/>
@@ -31775,7 +31775,7 @@
         <v>tanmay.iyer.0001@example.com</v>
       </c>
       <c r="W392" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000001&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X392" t="str">
         <v/>
@@ -31855,7 +31855,7 @@
         <v>karan.kapoor.0002@example.com</v>
       </c>
       <c r="W393" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000002&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X393" t="str">
         <v/>
@@ -31935,7 +31935,7 @@
         <v>isha.kulkarni.0003@example.com</v>
       </c>
       <c r="W394" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000003&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X394" t="str">
         <v/>
@@ -32015,7 +32015,7 @@
         <v>sneha.gupta.0004@example.com</v>
       </c>
       <c r="W395" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000004&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X395" t="str">
         <v/>
@@ -32095,7 +32095,7 @@
         <v>megha.mukherjee.0005@example.com</v>
       </c>
       <c r="W396" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000005&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X396" t="str">
         <v/>
@@ -32175,7 +32175,7 @@
         <v>pooja.kulkarni.0006@example.com</v>
       </c>
       <c r="W397" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000006&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X397" t="str">
         <v/>
@@ -32255,7 +32255,7 @@
         <v>vivek.kulkarni.0007@example.com</v>
       </c>
       <c r="W398" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000007&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X398" t="str">
         <v/>
@@ -32415,7 +32415,7 @@
         <v>siddharth.banerjee.0009@example.com</v>
       </c>
       <c r="W400" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000009&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X400" t="str">
         <v/>
@@ -32495,7 +32495,7 @@
         <v>harsh.kulkarni.0010@example.com</v>
       </c>
       <c r="W401" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000010&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X401" t="str">
         <v/>
@@ -32575,7 +32575,7 @@
         <v>sandeep.banerjee.0011@example.com</v>
       </c>
       <c r="W402" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000011&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X402" t="str">
         <v/>
@@ -32655,7 +32655,7 @@
         <v>kavya.joshi.0012@example.com</v>
       </c>
       <c r="W403" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000012&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X403" t="str">
         <v/>
@@ -32735,7 +32735,7 @@
         <v>geeta.krishnan.0013@example.com</v>
       </c>
       <c r="W404" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000013&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X404" t="str">
         <v/>
@@ -32815,7 +32815,7 @@
         <v>nikhil.banerjee.0014@example.com</v>
       </c>
       <c r="W405" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000014&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X405" t="str">
         <v/>
@@ -32895,7 +32895,7 @@
         <v>maya.menon.0015@example.com</v>
       </c>
       <c r="W406" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000015&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X406" t="str">
         <v/>
@@ -33055,7 +33055,7 @@
         <v>aarti.trivedi.0017@example.com</v>
       </c>
       <c r="W408" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000017&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X408" t="str">
         <v/>
@@ -33215,7 +33215,7 @@
         <v>lakshmi.singh.0019@example.com</v>
       </c>
       <c r="W410" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000019&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X410" t="str">
         <v/>
@@ -33295,7 +33295,7 @@
         <v>harsh.mehta.0020@example.com</v>
       </c>
       <c r="W411" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000020&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X411" t="str">
         <v/>
@@ -33375,7 +33375,7 @@
         <v>divya.bhattacharya.0021@example.com</v>
       </c>
       <c r="W412" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000021&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X412" t="str">
         <v/>
@@ -33455,7 +33455,7 @@
         <v>rahul.menon.0022@example.com</v>
       </c>
       <c r="W413" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000022&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X413" t="str">
         <v/>
@@ -33535,7 +33535,7 @@
         <v>varun.reddy.0023@example.com</v>
       </c>
       <c r="W414" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000023&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X414" t="str">
         <v/>
@@ -33615,7 +33615,7 @@
         <v>megha.iyer.0024@example.com</v>
       </c>
       <c r="W415" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000024&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X415" t="str">
         <v/>
@@ -33775,7 +33775,7 @@
         <v>megha.joshi.0026@example.com</v>
       </c>
       <c r="W417" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000026&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X417" t="str">
         <v/>
@@ -33855,7 +33855,7 @@
         <v>maya.iyer.0027@example.com</v>
       </c>
       <c r="W418" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000027&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X418" t="str">
         <v/>
@@ -33935,7 +33935,7 @@
         <v>sunita.bhandari.0028@example.com</v>
       </c>
       <c r="W419" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000028&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X419" t="str">
         <v/>
@@ -34015,7 +34015,7 @@
         <v>ritu.verma.0029@example.com</v>
       </c>
       <c r="W420" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000029&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X420" t="str">
         <v/>
@@ -34095,7 +34095,7 @@
         <v>sandeep.sharma.0030@example.com</v>
       </c>
       <c r="W421" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000030&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X421" t="str">
         <v>AMNS-V000001</v>
@@ -34175,7 +34175,7 @@
         <v>sandeep.verma.0031@example.com</v>
       </c>
       <c r="W422" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000031&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X422" t="str">
         <v/>
@@ -34255,7 +34255,7 @@
         <v>vikram.kapoor.0032@example.com</v>
       </c>
       <c r="W423" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000032&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X423" t="str">
         <v/>
@@ -34335,7 +34335,7 @@
         <v>riya.choudhury.0033@example.com</v>
       </c>
       <c r="W424" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000033&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X424" t="str">
         <v/>
@@ -34415,7 +34415,7 @@
         <v>shweta.joshi.0034@example.com</v>
       </c>
       <c r="W425" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000034&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X425" t="str">
         <v/>
@@ -34495,7 +34495,7 @@
         <v>rohit.kulkarni.0035@example.com</v>
       </c>
       <c r="W426" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000035&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X426" t="str">
         <v/>
@@ -34575,7 +34575,7 @@
         <v>lakshmi.mukherjee.0036@example.com</v>
       </c>
       <c r="W427" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000036&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X427" t="str">
         <v/>
@@ -34655,7 +34655,7 @@
         <v>ramesh.iyer.0037@example.com</v>
       </c>
       <c r="W428" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000037&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X428" t="str">
         <v/>
@@ -34735,7 +34735,7 @@
         <v>deepak.gupta.0038@example.com</v>
       </c>
       <c r="W429" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000038&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X429" t="str">
         <v/>
@@ -34975,7 +34975,7 @@
         <v>rahul.saxena.0041@example.com</v>
       </c>
       <c r="W432" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000041&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X432" t="str">
         <v/>
@@ -35055,7 +35055,7 @@
         <v>neha.choudhury.0042@example.com</v>
       </c>
       <c r="W433" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000042&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X433" t="str">
         <v/>
@@ -35135,7 +35135,7 @@
         <v>tanmay.chatterjee.0043@example.com</v>
       </c>
       <c r="W434" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000043&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X434" t="str">
         <v>AMNS-V000001</v>
@@ -35215,7 +35215,7 @@
         <v>ananya.agarwal.0044@example.com</v>
       </c>
       <c r="W435" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000044&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X435" t="str">
         <v/>
@@ -35295,7 +35295,7 @@
         <v>suresh.agarwal.0045@example.com</v>
       </c>
       <c r="W436" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000045&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X436" t="str">
         <v/>
@@ -35375,7 +35375,7 @@
         <v>tara.sharma.0046@example.com</v>
       </c>
       <c r="W437" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000046&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X437" t="str">
         <v/>
@@ -35455,7 +35455,7 @@
         <v>aditya.das.0047@example.com</v>
       </c>
       <c r="W438" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000047&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X438" t="str">
         <v/>
@@ -35535,7 +35535,7 @@
         <v>anjali.tiwari.0048@example.com</v>
       </c>
       <c r="W439" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000048&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X439" t="str">
         <v>AMNS-V000001</v>
@@ -35615,7 +35615,7 @@
         <v>roshni.mukherjee.0049@example.com</v>
       </c>
       <c r="W440" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000049&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X440" t="str">
         <v/>
@@ -35695,7 +35695,7 @@
         <v>rahul.das.0050@example.com</v>
       </c>
       <c r="W441" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000050&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X441" t="str">
         <v/>
@@ -35775,7 +35775,7 @@
         <v>tanmay.kulkarni.0051@example.com</v>
       </c>
       <c r="W442" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000051&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X442" t="str">
         <v/>
@@ -35855,7 +35855,7 @@
         <v>varun.mukherjee.0052@example.com</v>
       </c>
       <c r="W443" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000052&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X443" t="str">
         <v/>
@@ -35935,7 +35935,7 @@
         <v>sandeep.joshi.0053@example.com</v>
       </c>
       <c r="W444" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000053&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X444" t="str">
         <v/>
@@ -36095,7 +36095,7 @@
         <v>swati.tiwari.0055@example.com</v>
       </c>
       <c r="W446" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000055&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X446" t="str">
         <v/>
@@ -36255,7 +36255,7 @@
         <v>vivek.nair.0057@example.com</v>
       </c>
       <c r="W448" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000057&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X448" t="str">
         <v/>
@@ -36335,7 +36335,7 @@
         <v>rahul.choudhury.0058@example.com</v>
       </c>
       <c r="W449" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000058&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X449" t="str">
         <v/>
@@ -36415,7 +36415,7 @@
         <v>arjun.kapoor.0059@example.com</v>
       </c>
       <c r="W450" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000059&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X450" t="str">
         <v/>
@@ -36575,7 +36575,7 @@
         <v>sunita.gupta.0061@example.com</v>
       </c>
       <c r="W452" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000061&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X452" t="str">
         <v/>
@@ -36735,7 +36735,7 @@
         <v>lakshmi.kapoor.0063@example.com</v>
       </c>
       <c r="W454" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000063&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X454" t="str">
         <v/>
@@ -36815,7 +36815,7 @@
         <v>ramesh.banerjee.0064@example.com</v>
       </c>
       <c r="W455" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000064&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X455" t="str">
         <v/>
@@ -36975,7 +36975,7 @@
         <v>isha.singh.0066@example.com</v>
       </c>
       <c r="W457" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000066&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X457" t="str">
         <v>AMNS-V000001</v>
@@ -37055,7 +37055,7 @@
         <v>karan.tiwari.0067@example.com</v>
       </c>
       <c r="W458" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000067&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X458" t="str">
         <v/>
@@ -37135,7 +37135,7 @@
         <v>madhuri.tiwari.0068@example.com</v>
       </c>
       <c r="W459" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000068&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X459" t="str">
         <v/>
@@ -37215,7 +37215,7 @@
         <v>pallavi.iyer.0069@example.com</v>
       </c>
       <c r="W460" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000069&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X460" t="str">
         <v/>
@@ -37295,7 +37295,7 @@
         <v>divya.chatterjee.0070@example.com</v>
       </c>
       <c r="W461" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000070&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X461" t="str">
         <v/>
@@ -37375,7 +37375,7 @@
         <v>kavya.gupta.0071@example.com</v>
       </c>
       <c r="W462" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000071&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X462" t="str">
         <v/>
@@ -37455,7 +37455,7 @@
         <v>neha.desai.0072@example.com</v>
       </c>
       <c r="W463" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000072&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X463" t="str">
         <v/>
@@ -37535,7 +37535,7 @@
         <v>neha.kulkarni.0073@example.com</v>
       </c>
       <c r="W464" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000073&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X464" t="str">
         <v/>
@@ -37615,7 +37615,7 @@
         <v>kunal.singh.0074@example.com</v>
       </c>
       <c r="W465" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000074&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X465" t="str">
         <v/>
@@ -37695,7 +37695,7 @@
         <v>neha.patel.0075@example.com</v>
       </c>
       <c r="W466" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000075&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X466" t="str">
         <v/>
@@ -37855,7 +37855,7 @@
         <v>karan.singh.0077@example.com</v>
       </c>
       <c r="W468" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000077&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X468" t="str">
         <v/>
@@ -37935,7 +37935,7 @@
         <v>siddharth.nair.0078@example.com</v>
       </c>
       <c r="W469" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000078&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X469" t="str">
         <v/>
@@ -38015,7 +38015,7 @@
         <v>vikram.das.0079@example.com</v>
       </c>
       <c r="W470" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000079&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X470" t="str">
         <v>AMNS-V000001</v>
@@ -38175,7 +38175,7 @@
         <v>ritu.menon.0081@example.com</v>
       </c>
       <c r="W472" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000081&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X472" t="str">
         <v/>
@@ -38255,7 +38255,7 @@
         <v>pooja.roy.0082@example.com</v>
       </c>
       <c r="W473" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000082&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X473" t="str">
         <v/>
@@ -38335,7 +38335,7 @@
         <v>siddharth.mukherjee.0083@example.com</v>
       </c>
       <c r="W474" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000083&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X474" t="str">
         <v/>
@@ -38415,7 +38415,7 @@
         <v>roshni.pillai.0084@example.com</v>
       </c>
       <c r="W475" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000084&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X475" t="str">
         <v/>
@@ -38575,7 +38575,7 @@
         <v>sunita.das.0086@example.com</v>
       </c>
       <c r="W477" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000086&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X477" t="str">
         <v/>
@@ -38655,7 +38655,7 @@
         <v>swati.banerjee.0087@example.com</v>
       </c>
       <c r="W478" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000087&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X478" t="str">
         <v/>
@@ -38735,7 +38735,7 @@
         <v>pranav.reddy.0088@example.com</v>
       </c>
       <c r="W479" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000088&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X479" t="str">
         <v/>
@@ -38815,7 +38815,7 @@
         <v>pranav.agarwal.0089@example.com</v>
       </c>
       <c r="W480" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000089&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X480" t="str">
         <v/>
@@ -38895,7 +38895,7 @@
         <v>vivek.reddy.0090@example.com</v>
       </c>
       <c r="W481" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000090&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X481" t="str">
         <v/>
@@ -38975,7 +38975,7 @@
         <v>varun.bhattacharya.0091@example.com</v>
       </c>
       <c r="W482" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000091&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X482" t="str">
         <v/>
@@ -39055,7 +39055,7 @@
         <v>nikhil.krishnan.0092@example.com</v>
       </c>
       <c r="W483" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000092&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X483" t="str">
         <v/>
@@ -39135,7 +39135,7 @@
         <v>priya.nair.0093@example.com</v>
       </c>
       <c r="W484" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000093&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X484" t="str">
         <v/>
@@ -39215,7 +39215,7 @@
         <v>anjali.kulkarni.0094@example.com</v>
       </c>
       <c r="W485" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000094&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X485" t="str">
         <v/>
@@ -39295,7 +39295,7 @@
         <v>anil.gupta.0095@example.com</v>
       </c>
       <c r="W486" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000095&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X486" t="str">
         <v>AMNS-V000001</v>
@@ -39375,7 +39375,7 @@
         <v>karan.desai.0096@example.com</v>
       </c>
       <c r="W487" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000096&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X487" t="str">
         <v>AMNS-V000001</v>
@@ -39455,7 +39455,7 @@
         <v>varun.banerjee.0097@example.com</v>
       </c>
       <c r="W488" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000097&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X488" t="str">
         <v/>
@@ -39535,7 +39535,7 @@
         <v>suresh.kapoor.0098@example.com</v>
       </c>
       <c r="W489" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000098&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X489" t="str">
         <v/>
@@ -39615,7 +39615,7 @@
         <v>akash.patel.0099@example.com</v>
       </c>
       <c r="W490" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000099&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X490" t="str">
         <v/>
@@ -39695,7 +39695,7 @@
         <v>aman.singh.0100@example.com</v>
       </c>
       <c r="W491" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000100&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X491" t="str">
         <v/>
@@ -39775,7 +39775,7 @@
         <v>manoj.kulkarni.0101@example.com</v>
       </c>
       <c r="W492" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000101&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X492" t="str">
         <v/>
@@ -39855,7 +39855,7 @@
         <v>vivek.bhattacharya.0102@example.com</v>
       </c>
       <c r="W493" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000102&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X493" t="str">
         <v/>
@@ -40015,7 +40015,7 @@
         <v>asha.joshi.0104@example.com</v>
       </c>
       <c r="W495" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000104&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X495" t="str">
         <v/>
@@ -40095,7 +40095,7 @@
         <v>yash.roy.0105@example.com</v>
       </c>
       <c r="W496" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000105&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X496" t="str">
         <v/>
@@ -40175,7 +40175,7 @@
         <v>riya.patel.0106@example.com</v>
       </c>
       <c r="W497" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000106&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X497" t="str">
         <v>AMNS-V000001</v>
@@ -40255,7 +40255,7 @@
         <v>shweta.chatterjee.0107@example.com</v>
       </c>
       <c r="W498" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000107&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X498" t="str">
         <v/>
@@ -40335,7 +40335,7 @@
         <v>harsh.agarwal.0108@example.com</v>
       </c>
       <c r="W499" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000108&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X499" t="str">
         <v/>
@@ -40415,7 +40415,7 @@
         <v>sanjay.chatterjee.0109@example.com</v>
       </c>
       <c r="W500" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000109&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X500" t="str">
         <v/>
@@ -40495,7 +40495,7 @@
         <v>lakshmi.menon.0110@example.com</v>
       </c>
       <c r="W501" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000110&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X501" t="str">
         <v/>
@@ -40575,7 +40575,7 @@
         <v>tanmay.gupta.0111@example.com</v>
       </c>
       <c r="W502" t="str">
-        <v>https://api.dicebear.com/9.x/initials/svg?seed=AMNS-E000111&amp;backgroundColor=2E3647&amp;textColor=ffffff</v>
+        <v/>
       </c>
       <c r="X502" t="str">
         <v/>

--- a/orglens_sample_template.xlsx
+++ b/orglens_sample_template.xlsx
@@ -403,7 +403,7 @@
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
@@ -424,7 +424,7 @@
     <col min="23" max="23" width="14.83203125" customWidth="1"/>
     <col min="24" max="24" width="23.83203125" customWidth="1"/>
     <col min="25" max="25" width="14.83203125" customWidth="1"/>
-    <col min="26" max="26" width="16.83203125" customWidth="1"/>
+    <col min="26" max="26" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
         <v>Line Manager Name</v>
       </c>
       <c r="E1" t="str">
-        <v>Job Title</v>
+        <v>Position Text</v>
       </c>
       <c r="F1" t="str">
         <v>Level</v>
@@ -504,7 +504,7 @@
         <v>Cohort Tags</v>
       </c>
       <c r="Z1" t="str">
-        <v>Current Status</v>
+        <v>Current Status/Tag</v>
       </c>
     </row>
     <row r="2">
